--- a/csv/export-fundanet/xarxes_socials.xlsx
+++ b/csv/export-fundanet/xarxes_socials.xlsx
@@ -46,6 +46,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -105,8 +106,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -127,49 +132,63 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1164</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>505</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>1395</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>767</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>288</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>2024</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>2025</v>
       </c>
     </row>
   </sheetData>

--- a/csv/export-fundanet/xarxes_socials.xlsx
+++ b/csv/export-fundanet/xarxes_socials.xlsx
@@ -106,12 +106,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -178,16 +182,16 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>-1</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="A4" s="2" t="n">
+        <v>1395</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>660</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>2025</v>
       </c>
     </row>
